--- a/xlsx/packagedata20260413 special cargo-HQ.xlsx
+++ b/xlsx/packagedata20260413 special cargo-HQ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963BAF72-531C-402F-B5FF-9D6BA2A33012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A478B7FF-BF0C-4430-BF50-9F9C8DE00A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,19 +91,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pkg01-54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pkg02-54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pkg03-54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pkg04-54</t>
+    <t>pkg01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
